--- a/samples/Trial_Balance_VM_Jul-26.xlsx
+++ b/samples/Trial_Balance_VM_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>16109295</v>
+        <v>747299.91</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>26302.5</v>
+        <v>25874.87</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>8888880</v>
+        <v>8744361.63</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>594277.5</v>
+        <v>584615.54</v>
       </c>
     </row>
     <row r="11">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>466860</v>
+        <v>459269.63</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>1092937.5</v>
+        <v>1075168.16</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D13">
-        <v>1620000</v>
+        <v>1571400</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +548,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D14">
-        <v>4606695</v>
+        <v>4531797.81</v>
       </c>
     </row>
     <row r="15">
@@ -562,7 +562,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D15">
-        <v>-1703475</v>
+        <v>-1675779.33</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D16">
-        <v>286140</v>
+        <v>281487.84</v>
       </c>
     </row>
     <row r="17">
@@ -590,7 +590,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D17">
-        <v>-2618115</v>
+        <v>-2575548.81</v>
       </c>
     </row>
     <row r="18">
@@ -604,7 +604,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D18">
-        <v>-1342500</v>
+        <v>-1320673.19</v>
       </c>
     </row>
     <row r="19">
@@ -618,7 +618,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D19">
-        <v>-645645</v>
+        <v>-635147.89</v>
       </c>
     </row>
     <row r="20">
@@ -632,7 +632,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D20">
-        <v>-518535</v>
+        <v>-510104.48</v>
       </c>
     </row>
     <row r="21">
@@ -646,7 +646,7 @@
         <v>Equity</v>
       </c>
       <c r="D21">
-        <v>-11306250</v>
+        <v>-2500000</v>
       </c>
     </row>
     <row r="22">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-6036000</v>
+        <v>-500000</v>
       </c>
     </row>
     <row r="23">
@@ -674,7 +674,7 @@
         <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-3100597.5</v>
+        <v>-3144522.63</v>
       </c>
     </row>
     <row r="24">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-22785780</v>
+        <v>-18486862.84</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-3660000</v>
+        <v>-2920000</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Other Income</v>
       </c>
       <c r="D26">
-        <v>-143355</v>
+        <v>-116308.69</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D27">
-        <v>8259705</v>
+        <v>6701373.99</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>7116705</v>
+        <v>5774019.99</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>661980</v>
+        <v>537086.44</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>934650</v>
+        <v>758312.7</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>727500</v>
+        <v>590245</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>1194885</v>
+        <v>969450.03</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>399090</v>
+        <v>323795.02</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>874350</v>
+        <v>709389.3</v>
       </c>
     </row>
     <row r="35">

--- a/samples/Trial_Balance_VM_Jul-26.xlsx
+++ b/samples/Trial_Balance_VM_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>747299.91</v>
+        <v>587800.85</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>Equity</v>
       </c>
       <c r="D21">
-        <v>-2500000</v>
+        <v>-4000000</v>
       </c>
     </row>
     <row r="22">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-500000</v>
+        <v>-1000000</v>
       </c>
     </row>
     <row r="23">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-18486862.84</v>
+        <v>-4364710.74</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-2920000</v>
+        <v>-3504000</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Other Income</v>
       </c>
       <c r="D26">
-        <v>-116308.69</v>
+        <v>-36729.06</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D27">
-        <v>6701373.99</v>
+        <v>2006750.25</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>5774019.99</v>
+        <v>1734035.15</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>537086.44</v>
+        <v>161125.93</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>758312.7</v>
+        <v>227493.81</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>590245</v>
+        <v>175248</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>969450.03</v>
+        <v>292664.16</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>323795.02</v>
+        <v>95305.71</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>709389.3</v>
+        <v>212816.79</v>
       </c>
     </row>
     <row r="35">

--- a/samples/Trial_Balance_VM_Jul-26.xlsx
+++ b/samples/Trial_Balance_VM_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>587800.85</v>
+        <v>1765483.36</v>
       </c>
     </row>
     <row r="8">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-4364710.74</v>
+        <v>-5542393.25</v>
       </c>
     </row>
     <row r="25">
